--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/31,08,26 Останкино КИ и ЗПФ/машина САП 08,09 Бердянск_Грация КИ+ЗПФ/Заказ ЛП_Грация 08.09_с. Трояны.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/31,08,26 Останкино КИ и ЗПФ/машина САП 08,09 Бердянск_Грация КИ+ЗПФ/Заказ ЛП_Грация 08.09_с. Трояны.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\02,09 Грация\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\31,08,26 Останкино КИ и ЗПФ\машина САП 08,09 Бердянск_Грация КИ+ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1F13AC-0DB0-4906-83AB-F7EBE772CE74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1751094A-0F66-46EE-B884-6F7AE0FAAD12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6259,7 +6259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BO1692"/>
@@ -6485,7 +6485,7 @@
       <c r="BN9" s="120"/>
       <c r="BO9" s="120"/>
     </row>
-    <row r="10" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48"/>
       <c r="B10" s="43" t="s">
         <v>18</v>
@@ -6499,7 +6499,7 @@
       <c r="I10" s="43"/>
       <c r="J10" s="44"/>
     </row>
-    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A11" s="58">
         <v>4561</v>
       </c>
@@ -6585,7 +6585,7 @@
       <c r="BN11" s="121"/>
       <c r="BO11" s="121"/>
     </row>
-    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="145">
         <v>7536</v>
       </c>
@@ -6673,7 +6673,7 @@
       <c r="BN12" s="121"/>
       <c r="BO12" s="121"/>
     </row>
-    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58">
         <v>5851</v>
       </c>
@@ -6849,7 +6849,7 @@
       <c r="BN14" s="121"/>
       <c r="BO14" s="121"/>
     </row>
-    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:67" s="15" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58">
         <v>4574</v>
       </c>
@@ -7069,7 +7069,7 @@
       <c r="J18" s="29"/>
       <c r="L18" s="122"/>
     </row>
-    <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="58">
         <v>6861</v>
       </c>
@@ -7099,7 +7099,7 @@
       <c r="J19" s="29"/>
       <c r="L19" s="122"/>
     </row>
-    <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58">
         <v>6862</v>
       </c>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="L21" s="122"/>
     </row>
-    <row r="22" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="58">
         <v>7334</v>
       </c>
@@ -7225,7 +7225,7 @@
       <c r="J23" s="29"/>
       <c r="L23" s="122"/>
     </row>
-    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="58">
         <v>8014</v>
       </c>
@@ -7491,7 +7491,7 @@
       <c r="BN26" s="122"/>
       <c r="BO26" s="122"/>
     </row>
-    <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="147">
         <v>6340</v>
       </c>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L27" s="122"/>
     </row>
-    <row r="28" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="147">
         <v>6341</v>
       </c>
@@ -7619,7 +7619,7 @@
       <c r="J30" s="61"/>
       <c r="L30" s="122"/>
     </row>
-    <row r="31" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="58">
         <v>7343</v>
       </c>
@@ -7649,7 +7649,7 @@
       <c r="J31" s="29"/>
       <c r="L31" s="122"/>
     </row>
-    <row r="32" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="58">
         <v>6797</v>
       </c>
@@ -7735,7 +7735,7 @@
       <c r="BN32" s="122"/>
       <c r="BO32" s="122"/>
     </row>
-    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="58">
         <v>7231</v>
       </c>
@@ -7821,7 +7821,7 @@
       <c r="BN33" s="122"/>
       <c r="BO33" s="122"/>
     </row>
-    <row r="34" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="48" t="s">
         <v>104</v>
       </c>
@@ -7838,7 +7838,7 @@
       <c r="J34" s="44"/>
       <c r="L34" s="122"/>
     </row>
-    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="58">
         <v>6767</v>
       </c>
@@ -7924,7 +7924,7 @@
       <c r="BN35" s="122"/>
       <c r="BO35" s="122"/>
     </row>
-    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="58">
         <v>6761</v>
       </c>
@@ -8010,7 +8010,7 @@
       <c r="BN36" s="122"/>
       <c r="BO36" s="122"/>
     </row>
-    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="58">
         <v>6764</v>
       </c>
@@ -8096,7 +8096,7 @@
       <c r="BN37" s="122"/>
       <c r="BO37" s="122"/>
     </row>
-    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="58">
         <v>6254</v>
       </c>
@@ -8182,7 +8182,7 @@
       <c r="BN38" s="122"/>
       <c r="BO38" s="122"/>
     </row>
-    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="58">
         <v>7075</v>
       </c>
@@ -8268,7 +8268,7 @@
       <c r="BN39" s="122"/>
       <c r="BO39" s="122"/>
     </row>
-    <row r="40" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="58">
         <v>7083</v>
       </c>
@@ -8354,7 +8354,7 @@
       <c r="BN40" s="122"/>
       <c r="BO40" s="122"/>
     </row>
-    <row r="41" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="58">
         <v>6829</v>
       </c>
@@ -8440,7 +8440,7 @@
       <c r="BN41" s="122"/>
       <c r="BO41" s="122"/>
     </row>
-    <row r="42" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="58">
         <v>7070</v>
       </c>
@@ -8526,7 +8526,7 @@
       <c r="BN42" s="122"/>
       <c r="BO42" s="122"/>
     </row>
-    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="58">
         <v>7076</v>
       </c>
@@ -8612,7 +8612,7 @@
       <c r="BN43" s="122"/>
       <c r="BO43" s="122"/>
     </row>
-    <row r="44" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="58">
         <v>7271</v>
       </c>
@@ -8874,7 +8874,7 @@
       <c r="BN46" s="122"/>
       <c r="BO46" s="122"/>
     </row>
-    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="58">
         <v>6759</v>
       </c>
@@ -8960,7 +8960,7 @@
       <c r="BN47" s="122"/>
       <c r="BO47" s="122"/>
     </row>
-    <row r="48" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="58">
         <v>6762</v>
       </c>
@@ -9046,7 +9046,7 @@
       <c r="BN48" s="122"/>
       <c r="BO48" s="122"/>
     </row>
-    <row r="49" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="58">
         <v>6765</v>
       </c>
@@ -9132,7 +9132,7 @@
       <c r="BN49" s="122"/>
       <c r="BO49" s="122"/>
     </row>
-    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="58">
         <v>7074</v>
       </c>
@@ -9218,7 +9218,7 @@
       <c r="BN50" s="122"/>
       <c r="BO50" s="122"/>
     </row>
-    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="58">
         <v>7123</v>
       </c>
@@ -9480,7 +9480,7 @@
       <c r="BN53" s="122"/>
       <c r="BO53" s="122"/>
     </row>
-    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="147">
         <v>7284</v>
       </c>
@@ -9568,7 +9568,7 @@
       <c r="BN54" s="122"/>
       <c r="BO54" s="122"/>
     </row>
-    <row r="55" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="58">
         <v>7461</v>
       </c>
@@ -9656,7 +9656,7 @@
       <c r="BN55" s="122"/>
       <c r="BO55" s="122"/>
     </row>
-    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="58">
         <v>7601</v>
       </c>
@@ -9742,7 +9742,7 @@
       <c r="BN56" s="122"/>
       <c r="BO56" s="122"/>
     </row>
-    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="147">
         <v>7371</v>
       </c>
@@ -10078,7 +10078,7 @@
       <c r="J63" s="29"/>
       <c r="L63" s="122"/>
     </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="58">
         <v>6602</v>
       </c>
@@ -10108,7 +10108,7 @@
       <c r="J64" s="29"/>
       <c r="L64" s="122"/>
     </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="145">
         <v>7040</v>
       </c>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="L65" s="122"/>
     </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="145">
         <v>7521</v>
       </c>
@@ -10204,7 +10204,7 @@
       <c r="J67" s="29"/>
       <c r="L67" s="122"/>
     </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="58">
         <v>7276</v>
       </c>
@@ -10266,7 +10266,7 @@
       <c r="J69" s="29"/>
       <c r="L69" s="122"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="58">
         <v>7044</v>
       </c>
@@ -10296,7 +10296,7 @@
       <c r="J70" s="29"/>
       <c r="L70" s="122"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="147">
         <v>7385</v>
       </c>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="L71" s="122"/>
     </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="147">
         <v>7460</v>
       </c>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="L72" s="122"/>
     </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="s">
         <v>104</v>
       </c>
@@ -10377,7 +10377,7 @@
       <c r="J73" s="44"/>
       <c r="L73" s="122"/>
     </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A74" s="58">
         <v>6527</v>
       </c>
@@ -10439,7 +10439,7 @@
       <c r="J75" s="29"/>
       <c r="L75" s="122"/>
     </row>
-    <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="58">
         <v>6549</v>
       </c>
@@ -10469,7 +10469,7 @@
       <c r="J76" s="29"/>
       <c r="L76" s="122"/>
     </row>
-    <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="58">
         <v>7001</v>
       </c>
@@ -10531,7 +10531,7 @@
       <c r="J78" s="29"/>
       <c r="L78" s="122"/>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="58">
         <v>7059</v>
       </c>
@@ -10561,7 +10561,7 @@
       <c r="J79" s="29"/>
       <c r="L79" s="122"/>
     </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="58">
         <v>6609</v>
       </c>
@@ -10591,7 +10591,7 @@
       <c r="J80" s="29"/>
       <c r="L80" s="122"/>
     </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="s">
         <v>104</v>
       </c>
@@ -10608,7 +10608,7 @@
       <c r="J81" s="44"/>
       <c r="L81" s="122"/>
     </row>
-    <row r="82" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A82" s="145">
         <v>7564</v>
       </c>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="L82" s="122"/>
     </row>
-    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="58">
         <v>7133</v>
       </c>
@@ -10670,7 +10670,7 @@
       <c r="J83" s="61"/>
       <c r="L83" s="122"/>
     </row>
-    <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="58">
         <v>6946</v>
       </c>
@@ -10700,7 +10700,7 @@
       <c r="J84" s="29"/>
       <c r="L84" s="122"/>
     </row>
-    <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="58">
         <v>7132</v>
       </c>
@@ -10762,7 +10762,7 @@
       <c r="J86" s="61"/>
       <c r="L86" s="122"/>
     </row>
-    <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="58">
         <v>7149</v>
       </c>
@@ -11052,7 +11052,7 @@
       <c r="J95" s="29"/>
       <c r="L95" s="122"/>
     </row>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="58">
         <v>7233</v>
       </c>
@@ -11114,7 +11114,7 @@
       <c r="J97" s="50"/>
       <c r="L97" s="122"/>
     </row>
-    <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="58">
         <v>7177</v>
       </c>
@@ -11240,7 +11240,7 @@
       <c r="J101" s="50"/>
       <c r="L101" s="122"/>
     </row>
-    <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="147">
         <v>7237</v>
       </c>
@@ -11304,7 +11304,7 @@
       <c r="J103" s="50"/>
       <c r="L103" s="122"/>
     </row>
-    <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="58">
         <v>7332</v>
       </c>
@@ -11334,7 +11334,7 @@
       <c r="J104" s="50"/>
       <c r="L104" s="122"/>
     </row>
-    <row r="105" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="58">
         <v>7333</v>
       </c>
@@ -11364,7 +11364,7 @@
       <c r="J105" s="50"/>
       <c r="L105" s="122"/>
     </row>
-    <row r="106" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="145">
         <v>7608</v>
       </c>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="L106" s="122"/>
     </row>
-    <row r="107" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:67" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="145">
         <v>7610</v>
       </c>
@@ -11428,7 +11428,7 @@
       </c>
       <c r="L107" s="122"/>
     </row>
-    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="48" t="s">
         <v>104</v>
       </c>
@@ -11501,7 +11501,7 @@
       <c r="BN108" s="122"/>
       <c r="BO108" s="122"/>
     </row>
-    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="58">
         <v>614</v>
       </c>
@@ -11739,7 +11739,7 @@
       <c r="J112" s="29"/>
       <c r="L112" s="122"/>
     </row>
-    <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="58">
         <v>7316</v>
       </c>
@@ -11769,7 +11769,7 @@
       <c r="J113" s="29"/>
       <c r="L113" s="122"/>
     </row>
-    <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="58">
         <v>7317</v>
       </c>
@@ -11863,7 +11863,7 @@
       <c r="J116" s="29"/>
       <c r="L116" s="122"/>
     </row>
-    <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="58">
         <v>7456</v>
       </c>
@@ -11893,7 +11893,7 @@
       <c r="J117" s="29"/>
       <c r="L117" s="122"/>
     </row>
-    <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="58">
         <v>7318</v>
       </c>
@@ -11955,7 +11955,7 @@
       <c r="J119" s="29"/>
       <c r="L119" s="122"/>
     </row>
-    <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="58">
         <v>7364</v>
       </c>
@@ -11985,7 +11985,7 @@
       <c r="J120" s="29"/>
       <c r="L120" s="122"/>
     </row>
-    <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="58">
         <v>7383</v>
       </c>
@@ -12079,7 +12079,7 @@
       <c r="J123" s="29"/>
       <c r="L123" s="122"/>
     </row>
-    <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="58">
         <v>6937</v>
       </c>
@@ -12173,7 +12173,7 @@
       <c r="J126" s="29"/>
       <c r="L126" s="122"/>
     </row>
-    <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="58">
         <v>6832</v>
       </c>
@@ -12203,7 +12203,7 @@
       <c r="J127" s="29"/>
       <c r="L127" s="122"/>
     </row>
-    <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="58">
         <v>7299</v>
       </c>
@@ -12265,7 +12265,7 @@
       <c r="J129" s="29"/>
       <c r="L129" s="122"/>
     </row>
-    <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="58">
         <v>5679</v>
       </c>
@@ -12427,7 +12427,7 @@
       <c r="J134" s="29"/>
       <c r="L134" s="122"/>
     </row>
-    <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="58">
         <v>6222</v>
       </c>
@@ -12457,7 +12457,7 @@
       <c r="J135" s="29"/>
       <c r="L135" s="122"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="147">
         <v>6834</v>
       </c>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="L136" s="122"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="147">
         <v>6965</v>
       </c>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="L137" s="122"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="147">
         <v>6557</v>
       </c>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="L138" s="122"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="145">
         <v>7626</v>
       </c>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L139" s="122"/>
     </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="48" t="s">
         <v>104</v>
       </c>
@@ -12602,7 +12602,7 @@
       <c r="J140" s="44"/>
       <c r="L140" s="122"/>
     </row>
-    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="58">
         <v>6470</v>
       </c>
@@ -12898,7 +12898,7 @@
       <c r="BN144" s="122"/>
       <c r="BO144" s="122"/>
     </row>
-    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="58">
         <v>6025</v>
       </c>
@@ -12984,7 +12984,7 @@
       <c r="BN145" s="122"/>
       <c r="BO145" s="122"/>
     </row>
-    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="63" customFormat="1" ht="16.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="58">
         <v>4584</v>
       </c>
@@ -13246,7 +13246,7 @@
       <c r="BN148" s="122"/>
       <c r="BO148" s="122"/>
     </row>
-    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:67" s="63" customFormat="1" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="58">
         <v>7377</v>
       </c>
@@ -13332,7 +13332,7 @@
       <c r="BN149" s="122"/>
       <c r="BO149" s="122"/>
     </row>
-    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="58">
         <v>6925</v>
       </c>
@@ -13418,7 +13418,7 @@
       <c r="BN150" s="122"/>
       <c r="BO150" s="122"/>
     </row>
-    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="145">
         <v>7647</v>
       </c>
@@ -13506,7 +13506,7 @@
       <c r="BN151" s="122"/>
       <c r="BO151" s="122"/>
     </row>
-    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A152" s="145">
         <v>7651</v>
       </c>
@@ -13594,7 +13594,7 @@
       <c r="BN152" s="122"/>
       <c r="BO152" s="122"/>
     </row>
-    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="48" t="s">
         <v>104</v>
       </c>
@@ -13667,7 +13667,7 @@
       <c r="BN153" s="122"/>
       <c r="BO153" s="122"/>
     </row>
-    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:67" s="63" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="145">
         <v>7485</v>
       </c>
@@ -13755,7 +13755,7 @@
       <c r="BN154" s="122"/>
       <c r="BO154" s="122"/>
     </row>
-    <row r="155" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="48" t="s">
         <v>104</v>
       </c>
@@ -13772,7 +13772,7 @@
       <c r="J155" s="44"/>
       <c r="L155" s="122"/>
     </row>
-    <row r="156" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:67" ht="16.5" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A156" s="58">
         <v>6620</v>
       </c>
@@ -13834,7 +13834,7 @@
       <c r="J157" s="29"/>
       <c r="L157" s="122"/>
     </row>
-    <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:67" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="145">
         <v>6008</v>
       </c>
@@ -13962,7 +13962,7 @@
       <c r="J161" s="29"/>
       <c r="L161" s="122"/>
     </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="58">
         <v>7092</v>
       </c>
@@ -13992,7 +13992,7 @@
       <c r="J162" s="29"/>
       <c r="L162" s="122"/>
     </row>
-    <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="58">
         <v>6448</v>
       </c>
@@ -14022,7 +14022,7 @@
       <c r="J163" s="29"/>
       <c r="L163" s="122"/>
     </row>
-    <row r="164" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="58">
         <v>6754</v>
       </c>
@@ -14052,7 +14052,7 @@
       <c r="J164" s="29"/>
       <c r="L164" s="122"/>
     </row>
-    <row r="165" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="58">
         <v>6208</v>
       </c>
@@ -29412,7 +29412,13 @@
       <c r="J1692" s="21"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:J168" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J168" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
